--- a/ig/nr-add-svs-profile/StructureDefinition-as-codeableconcept-timed.xlsx
+++ b/ig/nr-add-svs-profile/StructureDefinition-as-codeableconcept-timed.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-07T09:13:35+00:00</t>
+    <t>2024-02-07T12:54:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
